--- a/VENDA POR PAGAMENTO/VENDA POR PAGAMENTO.xlsx
+++ b/VENDA POR PAGAMENTO/VENDA POR PAGAMENTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Comercial\Desktop\Dre\VENDA POR PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12BE232-97D1-4A04-A818-A5BBB719AFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5FD79F-5EA2-43E0-84B6-69CAE57F3B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{256E494A-92E1-4818-8C67-991F5C0E7CA9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="30">
   <si>
     <t>unidade</t>
   </si>
@@ -125,6 +125,9 @@
   <si>
     <t>03</t>
   </si>
+  <si>
+    <t>2026-08</t>
+  </si>
 </sst>
 </file>
 
@@ -152,7 +155,6 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -530,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E89F85-4CA7-4ABF-9034-E58B70AE13CD}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -598,7 +600,7 @@
         <v>199386.31</v>
       </c>
       <c r="H2" s="4">
-        <v>2.66</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="I2" s="4">
         <v>1877</v>
@@ -697,7 +699,7 @@
         <v>13742.98</v>
       </c>
       <c r="H5" s="4">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I5" s="4">
         <v>72</v>
@@ -730,7 +732,7 @@
         <v>16474.400000000001</v>
       </c>
       <c r="H6" s="4">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I6" s="4">
         <v>288</v>
@@ -796,7 +798,7 @@
         <v>440.05</v>
       </c>
       <c r="H8" s="4">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4">
         <v>6</v>
@@ -829,7 +831,7 @@
         <v>189282.24</v>
       </c>
       <c r="H9" s="4">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="I9" s="4">
         <v>1861</v>
@@ -895,7 +897,7 @@
         <v>16272.23</v>
       </c>
       <c r="H11" s="4">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I11" s="4">
         <v>90</v>
@@ -928,7 +930,7 @@
         <v>22108.15</v>
       </c>
       <c r="H12" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="4">
         <v>327</v>
@@ -1027,7 +1029,7 @@
         <v>286662.7</v>
       </c>
       <c r="H15" s="4">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="I15" s="4">
         <v>3026</v>
@@ -1060,7 +1062,7 @@
         <v>430</v>
       </c>
       <c r="H16" s="4">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -1093,7 +1095,7 @@
         <v>2658.76</v>
       </c>
       <c r="H17" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="4">
         <v>362</v>
@@ -1126,7 +1128,7 @@
         <v>22079.39</v>
       </c>
       <c r="H18" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="4">
         <v>152</v>
@@ -1159,7 +1161,7 @@
         <v>26432.720000000001</v>
       </c>
       <c r="H19" s="4">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I19" s="4">
         <v>455</v>
@@ -1258,7 +1260,7 @@
         <v>345353.74</v>
       </c>
       <c r="H22" s="4">
-        <v>4.5999999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="I22" s="4">
         <v>3829</v>
@@ -1324,7 +1326,7 @@
         <v>2739.99</v>
       </c>
       <c r="H24" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I24" s="4">
         <v>387</v>
@@ -1357,7 +1359,7 @@
         <v>36685.96</v>
       </c>
       <c r="H25" s="4">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="I25" s="4">
         <v>211</v>
@@ -1390,7 +1392,7 @@
         <v>33644.42</v>
       </c>
       <c r="H26" s="4">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="I26" s="4">
         <v>533</v>
@@ -1456,7 +1458,7 @@
         <v>2684.42</v>
       </c>
       <c r="H28" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I28" s="4">
         <v>18</v>
@@ -1522,7 +1524,7 @@
         <v>388262.98</v>
       </c>
       <c r="H30" s="4">
-        <v>5.17</v>
+        <v>4.41</v>
       </c>
       <c r="I30" s="4">
         <v>4298</v>
@@ -1588,7 +1590,7 @@
         <v>33653.75</v>
       </c>
       <c r="H32" s="4">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="I32" s="4">
         <v>215</v>
@@ -1621,7 +1623,7 @@
         <v>41720.1</v>
       </c>
       <c r="H33" s="4">
-        <v>0.56000000000000005</v>
+        <v>0.47</v>
       </c>
       <c r="I33" s="4">
         <v>604</v>
@@ -1687,7 +1689,7 @@
         <v>4133.7</v>
       </c>
       <c r="H35" s="4">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I35" s="4">
         <v>28</v>
@@ -1753,7 +1755,7 @@
         <v>407895.21</v>
       </c>
       <c r="H37" s="4">
-        <v>5.43</v>
+        <v>4.63</v>
       </c>
       <c r="I37" s="4">
         <v>4167</v>
@@ -1786,7 +1788,7 @@
         <v>3031.72</v>
       </c>
       <c r="H38" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I38" s="4">
         <v>351</v>
@@ -1819,7 +1821,7 @@
         <v>42844.14</v>
       </c>
       <c r="H39" s="4">
-        <v>0.56999999999999995</v>
+        <v>0.49</v>
       </c>
       <c r="I39" s="4">
         <v>252</v>
@@ -1852,7 +1854,7 @@
         <v>38125.620000000003</v>
       </c>
       <c r="H40" s="4">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="I40" s="4">
         <v>613</v>
@@ -1885,7 +1887,7 @@
         <v>3073.37</v>
       </c>
       <c r="H41" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I41" s="4">
         <v>29</v>
@@ -1942,22 +1944,22 @@
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>15857.37</v>
+        <v>410149.02</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
       </c>
       <c r="G43" s="4">
-        <v>15857.37</v>
+        <v>410149.02</v>
       </c>
       <c r="H43" s="4">
-        <v>0.21</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="I43" s="4">
-        <v>145</v>
+        <v>4026</v>
       </c>
       <c r="J43" s="5">
-        <v>109.36</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -1975,22 +1977,22 @@
         <v>13</v>
       </c>
       <c r="E44" s="4">
-        <v>103.01</v>
+        <v>3512.83</v>
       </c>
       <c r="F44" s="4">
         <v>0</v>
       </c>
       <c r="G44" s="4">
-        <v>103.01</v>
+        <v>3512.83</v>
       </c>
       <c r="H44" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I44" s="4">
-        <v>14</v>
+        <v>431</v>
       </c>
       <c r="J44" s="5">
-        <v>7.36</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -2008,22 +2010,22 @@
         <v>14</v>
       </c>
       <c r="E45" s="4">
-        <v>2456.5100000000002</v>
+        <v>35113.019999999997</v>
       </c>
       <c r="F45" s="4">
         <v>0</v>
       </c>
       <c r="G45" s="4">
-        <v>2456.5100000000002</v>
+        <v>35113.019999999997</v>
       </c>
       <c r="H45" s="4">
-        <v>0.03</v>
+        <v>0.4</v>
       </c>
       <c r="I45" s="4">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="J45" s="5">
-        <v>272.95</v>
+        <v>169.63</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -2041,22 +2043,22 @@
         <v>15</v>
       </c>
       <c r="E46" s="4">
-        <v>1649.59</v>
+        <v>43465.68</v>
       </c>
       <c r="F46" s="4">
-        <v>120.37</v>
+        <v>6324.22</v>
       </c>
       <c r="G46" s="4">
-        <v>1529.22</v>
+        <v>37141.46</v>
       </c>
       <c r="H46" s="4">
-        <v>0.02</v>
+        <v>0.42</v>
       </c>
       <c r="I46" s="4">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="J46" s="5">
-        <v>66.489999999999995</v>
+        <v>71.56</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -2071,16 +2073,16 @@
         <v>27</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E47" s="4">
-        <v>45.18</v>
+        <v>170.8</v>
       </c>
       <c r="F47" s="4">
         <v>0</v>
       </c>
       <c r="G47" s="4">
-        <v>45.18</v>
+        <v>170.8</v>
       </c>
       <c r="H47" s="4">
         <v>0</v>
@@ -2089,205 +2091,205 @@
         <v>1</v>
       </c>
       <c r="J47" s="5">
-        <v>45.18</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="str">
         <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="4">
+        <v>47.89</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>47.89</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
         <v>1</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="4">
-        <v>674762.4</v>
-      </c>
-      <c r="F48" s="4">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <v>674762.4</v>
-      </c>
-      <c r="H48" s="4">
-        <v>8.99</v>
-      </c>
-      <c r="I48" s="4">
-        <v>8236</v>
-      </c>
       <c r="J48" s="5">
-        <v>81.93</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E49" s="4">
-        <v>3880.76</v>
+        <v>3889.82</v>
       </c>
       <c r="F49" s="4">
         <v>0</v>
       </c>
       <c r="G49" s="4">
-        <v>3880.76</v>
+        <v>3889.82</v>
       </c>
       <c r="H49" s="4">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I49" s="4">
-        <v>498</v>
+        <v>29</v>
       </c>
       <c r="J49" s="5">
-        <v>7.79</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E50" s="4">
-        <v>38340.97</v>
+        <v>800.9</v>
       </c>
       <c r="F50" s="4">
         <v>0</v>
       </c>
       <c r="G50" s="4">
-        <v>38340.97</v>
+        <v>800.9</v>
       </c>
       <c r="H50" s="4">
-        <v>0.51</v>
+        <v>0.01</v>
       </c>
       <c r="I50" s="4">
-        <v>333</v>
+        <v>15</v>
       </c>
       <c r="J50" s="5">
-        <v>115.14</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>93070.24</v>
+        <v>884.65</v>
       </c>
       <c r="F51" s="4">
-        <v>22544.46</v>
+        <v>0</v>
       </c>
       <c r="G51" s="4">
-        <v>70525.78</v>
+        <v>884.65</v>
       </c>
       <c r="H51" s="4">
-        <v>0.94</v>
+        <v>0.01</v>
       </c>
       <c r="I51" s="4">
-        <v>1461</v>
+        <v>12</v>
       </c>
       <c r="J51" s="5">
-        <v>48.27</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E52" s="4">
-        <v>441.04</v>
+        <v>20.18</v>
       </c>
       <c r="F52" s="4">
         <v>0</v>
       </c>
       <c r="G52" s="4">
-        <v>441.04</v>
+        <v>20.18</v>
       </c>
       <c r="H52" s="4">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I52" s="4">
         <v>1</v>
       </c>
       <c r="J52" s="5">
-        <v>441.04</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E53" s="4">
-        <v>3653.89</v>
+        <v>208.33</v>
       </c>
       <c r="F53" s="4">
         <v>0</v>
       </c>
       <c r="G53" s="4">
-        <v>3653.89</v>
+        <v>208.33</v>
       </c>
       <c r="H53" s="4">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I53" s="4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J53" s="5">
-        <v>98.75</v>
+        <v>208.33</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -2302,223 +2304,223 @@
         <v>10</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E54" s="4">
-        <v>1644.48</v>
+        <v>674762.4</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
       </c>
       <c r="G54" s="4">
-        <v>1644.48</v>
+        <v>674762.4</v>
       </c>
       <c r="H54" s="4">
-        <v>0.02</v>
+        <v>7.66</v>
       </c>
       <c r="I54" s="4">
-        <v>25</v>
+        <v>8236</v>
       </c>
       <c r="J54" s="5">
-        <v>65.78</v>
+        <v>81.93</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E55" s="4">
-        <v>698521.38</v>
+        <v>3880.76</v>
       </c>
       <c r="F55" s="4">
         <v>0</v>
       </c>
       <c r="G55" s="4">
-        <v>698521.38</v>
+        <v>3880.76</v>
       </c>
       <c r="H55" s="4">
-        <v>9.3000000000000007</v>
+        <v>0.04</v>
       </c>
       <c r="I55" s="4">
-        <v>8152</v>
+        <v>498</v>
       </c>
       <c r="J55" s="5">
-        <v>85.69</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" s="4">
-        <v>3713.66</v>
+        <v>38340.97</v>
       </c>
       <c r="F56" s="4">
         <v>0</v>
       </c>
       <c r="G56" s="4">
-        <v>3713.66</v>
+        <v>38340.97</v>
       </c>
       <c r="H56" s="4">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="I56" s="4">
-        <v>517</v>
+        <v>333</v>
       </c>
       <c r="J56" s="5">
-        <v>7.18</v>
+        <v>115.14</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" s="4">
-        <v>41042.1</v>
+        <v>93070.24</v>
       </c>
       <c r="F57" s="4">
-        <v>0</v>
+        <v>22544.46</v>
       </c>
       <c r="G57" s="4">
-        <v>41042.1</v>
+        <v>70525.78</v>
       </c>
       <c r="H57" s="4">
-        <v>0.55000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="I57" s="4">
-        <v>305</v>
+        <v>1461</v>
       </c>
       <c r="J57" s="5">
-        <v>134.56</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E58" s="4">
-        <v>95064.21</v>
+        <v>441.04</v>
       </c>
       <c r="F58" s="4">
-        <v>22506.87</v>
+        <v>0</v>
       </c>
       <c r="G58" s="4">
-        <v>72557.34</v>
+        <v>441.04</v>
       </c>
       <c r="H58" s="4">
-        <v>0.97</v>
+        <v>0.01</v>
       </c>
       <c r="I58" s="4">
-        <v>1402</v>
+        <v>1</v>
       </c>
       <c r="J58" s="5">
-        <v>51.75</v>
+        <v>441.04</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E59" s="4">
-        <v>55.96</v>
+        <v>3653.89</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
       </c>
       <c r="G59" s="4">
-        <v>55.96</v>
+        <v>3653.89</v>
       </c>
       <c r="H59" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I59" s="4">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J59" s="5">
-        <v>55.96</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E60" s="4">
-        <v>2943</v>
+        <v>1644.48</v>
       </c>
       <c r="F60" s="4">
         <v>0</v>
       </c>
       <c r="G60" s="4">
-        <v>2943</v>
+        <v>1644.48</v>
       </c>
       <c r="H60" s="4">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I60" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J60" s="5">
-        <v>105.11</v>
+        <v>65.78</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -2533,223 +2535,223 @@
         <v>18</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>2455.25</v>
+        <v>698521.38</v>
       </c>
       <c r="F61" s="4">
         <v>0</v>
       </c>
       <c r="G61" s="4">
-        <v>2455.25</v>
+        <v>698521.38</v>
       </c>
       <c r="H61" s="4">
-        <v>0.03</v>
+        <v>7.93</v>
       </c>
       <c r="I61" s="4">
-        <v>39</v>
+        <v>8152</v>
       </c>
       <c r="J61" s="5">
-        <v>62.96</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E62" s="4">
-        <v>851510.25</v>
+        <v>3713.66</v>
       </c>
       <c r="F62" s="4">
         <v>0</v>
       </c>
       <c r="G62" s="4">
-        <v>851510.25</v>
+        <v>3713.66</v>
       </c>
       <c r="H62" s="4">
-        <v>11.34</v>
+        <v>0.04</v>
       </c>
       <c r="I62" s="4">
-        <v>9684</v>
+        <v>517</v>
       </c>
       <c r="J62" s="5">
-        <v>87.93</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E63" s="4">
-        <v>4674.12</v>
+        <v>41042.1</v>
       </c>
       <c r="F63" s="4">
         <v>0</v>
       </c>
       <c r="G63" s="4">
-        <v>4674.12</v>
+        <v>41042.1</v>
       </c>
       <c r="H63" s="4">
-        <v>0.06</v>
+        <v>0.47</v>
       </c>
       <c r="I63" s="4">
-        <v>656</v>
+        <v>305</v>
       </c>
       <c r="J63" s="5">
-        <v>7.13</v>
+        <v>134.56</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E64" s="4">
-        <v>57214.36</v>
+        <v>95064.21</v>
       </c>
       <c r="F64" s="4">
-        <v>0</v>
+        <v>22506.87</v>
       </c>
       <c r="G64" s="4">
-        <v>57214.36</v>
+        <v>72557.34</v>
       </c>
       <c r="H64" s="4">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="I64" s="4">
-        <v>373</v>
+        <v>1402</v>
       </c>
       <c r="J64" s="5">
-        <v>153.38999999999999</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E65" s="4">
-        <v>112964.08</v>
+        <v>55.96</v>
       </c>
       <c r="F65" s="4">
-        <v>26690.03</v>
+        <v>0</v>
       </c>
       <c r="G65" s="4">
-        <v>86274.05</v>
+        <v>55.96</v>
       </c>
       <c r="H65" s="4">
-        <v>1.1499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I65" s="4">
-        <v>1602</v>
+        <v>1</v>
       </c>
       <c r="J65" s="5">
-        <v>53.85</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E66" s="4">
-        <v>103.76</v>
+        <v>2943</v>
       </c>
       <c r="F66" s="4">
         <v>0</v>
       </c>
       <c r="G66" s="4">
-        <v>103.76</v>
+        <v>2943</v>
       </c>
       <c r="H66" s="4">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I66" s="4">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J66" s="5">
-        <v>103.76</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="str">
-        <f t="shared" ref="A67:A100" si="1">RIGHT(C67,1)</f>
-        <v>3</v>
+        <f t="shared" ref="A67:A113" si="1">RIGHT(C67,1)</f>
+        <v>2</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E67" s="4">
-        <v>5938.26</v>
+        <v>2455.25</v>
       </c>
       <c r="F67" s="4">
         <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>5938.26</v>
+        <v>2455.25</v>
       </c>
       <c r="H67" s="4">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="I67" s="4">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J67" s="5">
-        <v>123.71</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -2764,223 +2766,223 @@
         <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E68" s="4">
-        <v>2093.71</v>
+        <v>851510.25</v>
       </c>
       <c r="F68" s="4">
         <v>0</v>
       </c>
       <c r="G68" s="4">
-        <v>2093.71</v>
+        <v>851510.25</v>
       </c>
       <c r="H68" s="4">
-        <v>0.03</v>
+        <v>9.66</v>
       </c>
       <c r="I68" s="4">
-        <v>35</v>
+        <v>9684</v>
       </c>
       <c r="J68" s="5">
-        <v>59.82</v>
+        <v>87.93</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E69" s="4">
-        <v>725127.34</v>
+        <v>4674.12</v>
       </c>
       <c r="F69" s="4">
         <v>0</v>
       </c>
       <c r="G69" s="4">
-        <v>725127.34</v>
+        <v>4674.12</v>
       </c>
       <c r="H69" s="4">
-        <v>9.66</v>
+        <v>0.05</v>
       </c>
       <c r="I69" s="4">
-        <v>8281</v>
+        <v>656</v>
       </c>
       <c r="J69" s="5">
-        <v>87.57</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E70" s="4">
-        <v>4675.7</v>
+        <v>57214.36</v>
       </c>
       <c r="F70" s="4">
         <v>0</v>
       </c>
       <c r="G70" s="4">
-        <v>4675.7</v>
+        <v>57214.36</v>
       </c>
       <c r="H70" s="4">
-        <v>0.06</v>
+        <v>0.65</v>
       </c>
       <c r="I70" s="4">
-        <v>632</v>
+        <v>373</v>
       </c>
       <c r="J70" s="5">
-        <v>7.4</v>
+        <v>153.38999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E71" s="4">
-        <v>37628.54</v>
+        <v>112964.08</v>
       </c>
       <c r="F71" s="4">
-        <v>0</v>
+        <v>26690.03</v>
       </c>
       <c r="G71" s="4">
-        <v>37628.54</v>
+        <v>86274.05</v>
       </c>
       <c r="H71" s="4">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="I71" s="4">
-        <v>275</v>
+        <v>1602</v>
       </c>
       <c r="J71" s="5">
-        <v>136.83000000000001</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E72" s="4">
-        <v>99752.08</v>
+        <v>103.76</v>
       </c>
       <c r="F72" s="4">
-        <v>24044.36</v>
+        <v>0</v>
       </c>
       <c r="G72" s="4">
-        <v>75707.72</v>
+        <v>103.76</v>
       </c>
       <c r="H72" s="4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4">
-        <v>1459</v>
+        <v>1</v>
       </c>
       <c r="J72" s="5">
-        <v>51.89</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E73" s="4">
-        <v>291.57</v>
+        <v>5938.26</v>
       </c>
       <c r="F73" s="4">
         <v>0</v>
       </c>
       <c r="G73" s="4">
-        <v>291.57</v>
+        <v>5938.26</v>
       </c>
       <c r="H73" s="4">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I73" s="4">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J73" s="5">
-        <v>97.19</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E74" s="4">
-        <v>7.35</v>
+        <v>2093.71</v>
       </c>
       <c r="F74" s="4">
         <v>0</v>
       </c>
       <c r="G74" s="4">
-        <v>7.35</v>
+        <v>2093.71</v>
       </c>
       <c r="H74" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I74" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J74" s="5">
-        <v>7.35</v>
+        <v>59.82</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -2995,25 +2997,25 @@
         <v>20</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>187.43</v>
+        <v>725127.34</v>
       </c>
       <c r="F75" s="4">
         <v>0</v>
       </c>
       <c r="G75" s="4">
-        <v>187.43</v>
+        <v>725127.34</v>
       </c>
       <c r="H75" s="4">
-        <v>0</v>
+        <v>8.23</v>
       </c>
       <c r="I75" s="4">
-        <v>1</v>
+        <v>8281</v>
       </c>
       <c r="J75" s="5">
-        <v>187.43</v>
+        <v>87.57</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3028,25 +3030,25 @@
         <v>20</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E76" s="4">
-        <v>3366.55</v>
+        <v>4675.7</v>
       </c>
       <c r="F76" s="4">
         <v>0</v>
       </c>
       <c r="G76" s="4">
-        <v>3366.55</v>
+        <v>4675.7</v>
       </c>
       <c r="H76" s="4">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I76" s="4">
-        <v>33</v>
+        <v>632</v>
       </c>
       <c r="J76" s="5">
-        <v>102.02</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -3061,223 +3063,223 @@
         <v>20</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E77" s="4">
-        <v>2148.54</v>
+        <v>37628.54</v>
       </c>
       <c r="F77" s="4">
         <v>0</v>
       </c>
       <c r="G77" s="4">
-        <v>2148.54</v>
+        <v>37628.54</v>
       </c>
       <c r="H77" s="4">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
       <c r="I77" s="4">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="J77" s="5">
-        <v>53.71</v>
+        <v>136.83000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E78" s="4">
-        <v>757197.58</v>
+        <v>99752.08</v>
       </c>
       <c r="F78" s="4">
-        <v>0</v>
+        <v>24044.36</v>
       </c>
       <c r="G78" s="4">
-        <v>757197.58</v>
+        <v>75707.72</v>
       </c>
       <c r="H78" s="4">
-        <v>10.09</v>
+        <v>0.86</v>
       </c>
       <c r="I78" s="4">
-        <v>8700</v>
+        <v>1459</v>
       </c>
       <c r="J78" s="5">
-        <v>87.03</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E79" s="4">
-        <v>2750</v>
+        <v>291.57</v>
       </c>
       <c r="F79" s="4">
         <v>0</v>
       </c>
       <c r="G79" s="4">
-        <v>2750</v>
+        <v>291.57</v>
       </c>
       <c r="H79" s="4">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I79" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J79" s="5">
-        <v>687.5</v>
+        <v>97.19</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E80" s="4">
-        <v>4433.8100000000004</v>
+        <v>7.35</v>
       </c>
       <c r="F80" s="4">
         <v>0</v>
       </c>
       <c r="G80" s="4">
-        <v>4433.8100000000004</v>
+        <v>7.35</v>
       </c>
       <c r="H80" s="4">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I80" s="4">
-        <v>601</v>
+        <v>1</v>
       </c>
       <c r="J80" s="5">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E81" s="4">
-        <v>42705.82</v>
+        <v>187.43</v>
       </c>
       <c r="F81" s="4">
         <v>0</v>
       </c>
       <c r="G81" s="4">
-        <v>42705.82</v>
+        <v>187.43</v>
       </c>
       <c r="H81" s="4">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="I81" s="4">
-        <v>292</v>
+        <v>1</v>
       </c>
       <c r="J81" s="5">
-        <v>146.25</v>
+        <v>187.43</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E82" s="4">
-        <v>109615.58</v>
+        <v>3366.55</v>
       </c>
       <c r="F82" s="4">
-        <v>26722.77</v>
+        <v>0</v>
       </c>
       <c r="G82" s="4">
-        <v>82892.81</v>
+        <v>3366.55</v>
       </c>
       <c r="H82" s="4">
-        <v>1.1000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I82" s="4">
-        <v>1569</v>
+        <v>33</v>
       </c>
       <c r="J82" s="5">
-        <v>52.83</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E83" s="4">
-        <v>191.98</v>
+        <v>2148.54</v>
       </c>
       <c r="F83" s="4">
         <v>0</v>
       </c>
       <c r="G83" s="4">
-        <v>191.98</v>
+        <v>2148.54</v>
       </c>
       <c r="H83" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I83" s="4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J83" s="5">
-        <v>32</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
@@ -3292,25 +3294,25 @@
         <v>22</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E84" s="4">
-        <v>216.57</v>
+        <v>757197.58</v>
       </c>
       <c r="F84" s="4">
         <v>0</v>
       </c>
       <c r="G84" s="4">
-        <v>216.57</v>
+        <v>757197.58</v>
       </c>
       <c r="H84" s="4">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="I84" s="4">
-        <v>4</v>
+        <v>8700</v>
       </c>
       <c r="J84" s="5">
-        <v>54.14</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
@@ -3325,25 +3327,25 @@
         <v>22</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E85" s="4">
-        <v>4202.47</v>
+        <v>2750</v>
       </c>
       <c r="F85" s="4">
         <v>0</v>
       </c>
       <c r="G85" s="4">
-        <v>4202.47</v>
+        <v>2750</v>
       </c>
       <c r="H85" s="4">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I85" s="4">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J85" s="5">
-        <v>110.59</v>
+        <v>687.5</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
@@ -3358,154 +3360,154 @@
         <v>22</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E86" s="4">
-        <v>2016.64</v>
+        <v>4433.8100000000004</v>
       </c>
       <c r="F86" s="4">
         <v>0</v>
       </c>
       <c r="G86" s="4">
-        <v>2016.64</v>
+        <v>4433.8100000000004</v>
       </c>
       <c r="H86" s="4">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I86" s="4">
-        <v>32</v>
+        <v>601</v>
       </c>
       <c r="J86" s="5">
-        <v>63.02</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E87" s="4">
-        <v>747057.91</v>
+        <v>42705.82</v>
       </c>
       <c r="F87" s="4">
         <v>0</v>
       </c>
       <c r="G87" s="4">
-        <v>747057.91</v>
+        <v>42705.82</v>
       </c>
       <c r="H87" s="4">
-        <v>9.9499999999999993</v>
+        <v>0.48</v>
       </c>
       <c r="I87" s="4">
-        <v>8425</v>
+        <v>292</v>
       </c>
       <c r="J87" s="5">
-        <v>88.67</v>
+        <v>146.25</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E88" s="4">
-        <v>4308.8999999999996</v>
+        <v>109615.58</v>
       </c>
       <c r="F88" s="4">
-        <v>0</v>
+        <v>26722.77</v>
       </c>
       <c r="G88" s="4">
-        <v>4308.8999999999996</v>
+        <v>82892.81</v>
       </c>
       <c r="H88" s="4">
-        <v>0.06</v>
+        <v>0.94</v>
       </c>
       <c r="I88" s="4">
-        <v>572</v>
+        <v>1569</v>
       </c>
       <c r="J88" s="5">
-        <v>7.53</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="str">
         <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" s="4">
+        <v>191.98</v>
+      </c>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="4">
+        <v>191.98</v>
+      </c>
+      <c r="H89" s="4">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4">
         <v>6</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" s="4">
-        <v>38668.19</v>
-      </c>
-      <c r="F89" s="4">
-        <v>0</v>
-      </c>
-      <c r="G89" s="4">
-        <v>38668.19</v>
-      </c>
-      <c r="H89" s="4">
-        <v>0.52</v>
-      </c>
-      <c r="I89" s="4">
-        <v>272</v>
-      </c>
       <c r="J89" s="5">
-        <v>142.16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E90" s="4">
-        <v>104131.34</v>
+        <v>216.57</v>
       </c>
       <c r="F90" s="4">
-        <v>23789.14</v>
+        <v>0</v>
       </c>
       <c r="G90" s="4">
-        <v>80342.2</v>
+        <v>216.57</v>
       </c>
       <c r="H90" s="4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="I90" s="4">
-        <v>1484</v>
+        <v>4</v>
       </c>
       <c r="J90" s="5">
         <v>54.14</v>
@@ -3514,67 +3516,67 @@
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E91" s="4">
-        <v>1506.56</v>
+        <v>4202.47</v>
       </c>
       <c r="F91" s="4">
         <v>0</v>
       </c>
       <c r="G91" s="4">
-        <v>1506.56</v>
+        <v>4202.47</v>
       </c>
       <c r="H91" s="4">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I91" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="J91" s="5">
-        <v>71.739999999999995</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E92" s="4">
-        <v>439.16</v>
+        <v>2016.64</v>
       </c>
       <c r="F92" s="4">
         <v>0</v>
       </c>
       <c r="G92" s="4">
-        <v>439.16</v>
+        <v>2016.64</v>
       </c>
       <c r="H92" s="4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I92" s="4">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J92" s="5">
-        <v>219.58</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -3589,25 +3591,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>3950.13</v>
+        <v>747057.91</v>
       </c>
       <c r="F93" s="4">
         <v>0</v>
       </c>
       <c r="G93" s="4">
-        <v>3950.13</v>
+        <v>747057.91</v>
       </c>
       <c r="H93" s="4">
-        <v>0.05</v>
+        <v>8.48</v>
       </c>
       <c r="I93" s="4">
-        <v>35</v>
+        <v>8425</v>
       </c>
       <c r="J93" s="5">
-        <v>112.86</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
@@ -3622,223 +3624,652 @@
         <v>23</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E94" s="4">
-        <v>8981.17</v>
+        <v>4308.8999999999996</v>
       </c>
       <c r="F94" s="4">
         <v>0</v>
       </c>
       <c r="G94" s="4">
-        <v>8981.17</v>
+        <v>4308.8999999999996</v>
       </c>
       <c r="H94" s="4">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="I94" s="4">
-        <v>47</v>
+        <v>572</v>
       </c>
       <c r="J94" s="5">
-        <v>191.09</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E95" s="4">
-        <v>28169.7</v>
+        <v>38668.19</v>
       </c>
       <c r="F95" s="4">
         <v>0</v>
       </c>
       <c r="G95" s="4">
-        <v>28169.7</v>
+        <v>38668.19</v>
       </c>
       <c r="H95" s="4">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="I95" s="4">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="J95" s="5">
-        <v>87.48</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E96" s="4">
-        <v>165.61</v>
+        <v>104131.34</v>
       </c>
       <c r="F96" s="4">
-        <v>0</v>
+        <v>23789.14</v>
       </c>
       <c r="G96" s="4">
-        <v>165.61</v>
+        <v>80342.2</v>
       </c>
       <c r="H96" s="4">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="I96" s="4">
-        <v>21</v>
+        <v>1484</v>
       </c>
       <c r="J96" s="5">
-        <v>7.89</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E97" s="4">
-        <v>3217.91</v>
+        <v>1506.56</v>
       </c>
       <c r="F97" s="4">
         <v>0</v>
       </c>
       <c r="G97" s="4">
-        <v>3217.91</v>
+        <v>1506.56</v>
       </c>
       <c r="H97" s="4">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I97" s="4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J97" s="5">
-        <v>536.32000000000005</v>
+        <v>71.739999999999995</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E98" s="4">
-        <v>4619.7</v>
+        <v>439.16</v>
       </c>
       <c r="F98" s="4">
-        <v>898.02</v>
+        <v>0</v>
       </c>
       <c r="G98" s="4">
-        <v>3721.68</v>
+        <v>439.16</v>
       </c>
       <c r="H98" s="4">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I98" s="4">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="J98" s="5">
-        <v>65.290000000000006</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E99" s="4">
-        <v>15.5</v>
+        <v>3950.13</v>
       </c>
       <c r="F99" s="4">
         <v>0</v>
       </c>
       <c r="G99" s="4">
-        <v>15.5</v>
+        <v>3950.13</v>
       </c>
       <c r="H99" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I99" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J99" s="5">
-        <v>15.5</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="4">
-        <v>74.98</v>
+        <v>8981.17</v>
       </c>
       <c r="F100" s="4">
         <v>0</v>
       </c>
       <c r="G100" s="4">
-        <v>74.98</v>
+        <v>8981.17</v>
       </c>
       <c r="H100" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I100" s="4">
+        <v>47</v>
+      </c>
+      <c r="J100" s="5">
+        <v>191.09</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="4">
+        <v>744338.73</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
+        <v>744338.73</v>
+      </c>
+      <c r="H101" s="4">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="I101" s="4">
+        <v>8321</v>
+      </c>
+      <c r="J101" s="5">
+        <v>89.45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="4">
+        <v>3959.54</v>
+      </c>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4">
+        <v>3959.54</v>
+      </c>
+      <c r="H102" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="I102" s="4">
+        <v>536</v>
+      </c>
+      <c r="J102" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="4">
+        <v>43058.99</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>43058.99</v>
+      </c>
+      <c r="H103" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="I103" s="4">
+        <v>248</v>
+      </c>
+      <c r="J103" s="5">
+        <v>173.62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="4">
+        <v>92036.49</v>
+      </c>
+      <c r="F104" s="4">
+        <v>23074.9</v>
+      </c>
+      <c r="G104" s="4">
+        <v>68961.59</v>
+      </c>
+      <c r="H104" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="I104" s="4">
+        <v>1296</v>
+      </c>
+      <c r="J104" s="5">
+        <v>53.21</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" s="4">
+        <v>273.26</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4">
+        <v>273.26</v>
+      </c>
+      <c r="H105" s="4">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4">
+        <v>7</v>
+      </c>
+      <c r="J105" s="5">
+        <v>39.04</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="4">
+        <v>20.52</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4">
+        <v>20.52</v>
+      </c>
+      <c r="H106" s="4">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4">
         <v>1</v>
       </c>
-      <c r="J100" s="5">
-        <v>74.98</v>
+      <c r="J106" s="5">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="4">
+        <v>4376.3599999999997</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>4376.3599999999997</v>
+      </c>
+      <c r="H107" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I107" s="4">
+        <v>38</v>
+      </c>
+      <c r="J107" s="5">
+        <v>115.17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="4">
+        <v>2172.27</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4">
+        <v>2172.27</v>
+      </c>
+      <c r="H108" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I108" s="4">
+        <v>38</v>
+      </c>
+      <c r="J108" s="5">
+        <v>57.17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="4">
+        <v>2101.6999999999998</v>
+      </c>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4">
+        <v>2101.6999999999998</v>
+      </c>
+      <c r="H109" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I109" s="4">
+        <v>28</v>
+      </c>
+      <c r="J109" s="5">
+        <v>75.06</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="4">
+        <v>34.86</v>
+      </c>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4">
+        <v>34.86</v>
+      </c>
+      <c r="H110" s="4">
+        <v>0</v>
+      </c>
+      <c r="I110" s="4">
+        <v>6</v>
+      </c>
+      <c r="J110" s="5">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="4">
+        <v>44.9</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4">
+        <v>44.9</v>
+      </c>
+      <c r="H111" s="4">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4">
+        <v>1</v>
+      </c>
+      <c r="J111" s="5">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="4">
+        <v>211.5</v>
+      </c>
+      <c r="F112" s="4">
+        <v>111.82</v>
+      </c>
+      <c r="G112" s="4">
+        <v>99.68</v>
+      </c>
+      <c r="H112" s="4">
+        <v>0</v>
+      </c>
+      <c r="I112" s="4">
+        <v>5</v>
+      </c>
+      <c r="J112" s="5">
+        <v>19.940000000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="4">
+        <v>109.96</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4">
+        <v>109.96</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0</v>
+      </c>
+      <c r="I113" s="4">
+        <v>1</v>
+      </c>
+      <c r="J113" s="5">
+        <v>109.96</v>
       </c>
     </row>
   </sheetData>

--- a/VENDA POR PAGAMENTO/VENDA POR PAGAMENTO.xlsx
+++ b/VENDA POR PAGAMENTO/VENDA POR PAGAMENTO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Comercial\Desktop\Dre\VENDA POR PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5FD79F-5EA2-43E0-84B6-69CAE57F3B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1597F9-1BB8-4FB1-ABEA-CB03EA57859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{256E494A-92E1-4818-8C67-991F5C0E7CA9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="31">
   <si>
     <t>unidade</t>
   </si>
@@ -128,6 +128,9 @@
   <si>
     <t>2026-08</t>
   </si>
+  <si>
+    <t>IQNUS</t>
+  </si>
 </sst>
 </file>
 
@@ -155,6 +158,7 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -210,13 +214,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E89F85-4CA7-4ABF-9034-E58B70AE13CD}">
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -591,22 +595,22 @@
         <v>11</v>
       </c>
       <c r="E2" s="4">
-        <v>199386.31</v>
+        <v>198555.56</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <v>199386.31</v>
+        <v>198555.56</v>
       </c>
       <c r="H2" s="4">
-        <v>2.2599999999999998</v>
+        <v>1.97</v>
       </c>
       <c r="I2" s="4">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="J2" s="5">
-        <v>106.23</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -657,22 +661,22 @@
         <v>13</v>
       </c>
       <c r="E4" s="4">
-        <v>2421</v>
+        <v>2382.7199999999998</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <v>2421</v>
+        <v>2382.7199999999998</v>
       </c>
       <c r="H4" s="4">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I4" s="4">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J4" s="5">
-        <v>8.7100000000000009</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -690,22 +694,22 @@
         <v>14</v>
       </c>
       <c r="E5" s="4">
-        <v>13742.98</v>
+        <v>12850.16</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>13742.98</v>
+        <v>12850.16</v>
       </c>
       <c r="H5" s="4">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I5" s="4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J5" s="5">
-        <v>190.87</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -723,22 +727,22 @@
         <v>15</v>
       </c>
       <c r="E6" s="4">
-        <v>19449.830000000002</v>
+        <v>19037.849999999999</v>
       </c>
       <c r="F6" s="4">
         <v>2975.43</v>
       </c>
       <c r="G6" s="4">
-        <v>16474.400000000001</v>
+        <v>16062.42</v>
       </c>
       <c r="H6" s="4">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="I6" s="4">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J6" s="5">
-        <v>57.2</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -822,22 +826,22 @@
         <v>11</v>
       </c>
       <c r="E9" s="4">
-        <v>189282.24</v>
+        <v>188007.13</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <v>189282.24</v>
+        <v>188007.13</v>
       </c>
       <c r="H9" s="4">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="I9" s="4">
-        <v>1861</v>
+        <v>1853</v>
       </c>
       <c r="J9" s="5">
-        <v>101.71</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -855,22 +859,22 @@
         <v>13</v>
       </c>
       <c r="E10" s="4">
-        <v>1675.29</v>
+        <v>1656.36</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>1675.29</v>
+        <v>1656.36</v>
       </c>
       <c r="H10" s="4">
         <v>0.02</v>
       </c>
       <c r="I10" s="4">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J10" s="5">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -888,22 +892,22 @@
         <v>14</v>
       </c>
       <c r="E11" s="4">
-        <v>16272.23</v>
+        <v>16229.8</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <v>16272.23</v>
+        <v>16229.8</v>
       </c>
       <c r="H11" s="4">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I11" s="4">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J11" s="5">
-        <v>180.8</v>
+        <v>184.43</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -921,22 +925,22 @@
         <v>15</v>
       </c>
       <c r="E12" s="4">
-        <v>26107.54</v>
+        <v>25614.03</v>
       </c>
       <c r="F12" s="4">
-        <v>3999.39</v>
+        <v>3962.21</v>
       </c>
       <c r="G12" s="4">
-        <v>22108.15</v>
+        <v>21651.82</v>
       </c>
       <c r="H12" s="4">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="I12" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J12" s="5">
-        <v>67.61</v>
+        <v>67.03</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -963,7 +967,7 @@
         <v>1419.26</v>
       </c>
       <c r="H13" s="4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I13" s="4">
         <v>11</v>
@@ -1020,22 +1024,22 @@
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>286662.7</v>
+        <v>283995.59000000003</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>286662.7</v>
+        <v>283995.59000000003</v>
       </c>
       <c r="H15" s="4">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="I15" s="4">
-        <v>3026</v>
+        <v>3006</v>
       </c>
       <c r="J15" s="5">
-        <v>94.73</v>
+        <v>94.48</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1086,22 +1090,22 @@
         <v>13</v>
       </c>
       <c r="E17" s="4">
-        <v>2658.76</v>
+        <v>2646.95</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>2658.76</v>
+        <v>2646.95</v>
       </c>
       <c r="H17" s="4">
         <v>0.03</v>
       </c>
       <c r="I17" s="4">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J17" s="5">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1119,22 +1123,22 @@
         <v>14</v>
       </c>
       <c r="E18" s="4">
-        <v>22079.39</v>
+        <v>21465.99</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <v>22079.39</v>
+        <v>21465.99</v>
       </c>
       <c r="H18" s="4">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="I18" s="4">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J18" s="5">
-        <v>145.26</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1152,22 +1156,22 @@
         <v>15</v>
       </c>
       <c r="E19" s="4">
-        <v>32148.48</v>
+        <v>31571.62</v>
       </c>
       <c r="F19" s="4">
-        <v>5715.76</v>
+        <v>5642.6</v>
       </c>
       <c r="G19" s="4">
-        <v>26432.720000000001</v>
+        <v>25929.02</v>
       </c>
       <c r="H19" s="4">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="I19" s="4">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="J19" s="5">
-        <v>58.09</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1218,22 +1222,22 @@
         <v>17</v>
       </c>
       <c r="E21" s="4">
-        <v>944.04</v>
+        <v>890.63</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <v>944.04</v>
+        <v>890.63</v>
       </c>
       <c r="H21" s="4">
         <v>0.01</v>
       </c>
       <c r="I21" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" s="5">
-        <v>59</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1251,22 +1255,22 @@
         <v>11</v>
       </c>
       <c r="E22" s="4">
-        <v>345353.74</v>
+        <v>343384.4</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <v>345353.74</v>
+        <v>343384.4</v>
       </c>
       <c r="H22" s="4">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="I22" s="4">
-        <v>3829</v>
+        <v>3805</v>
       </c>
       <c r="J22" s="5">
-        <v>90.19</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -1317,22 +1321,22 @@
         <v>13</v>
       </c>
       <c r="E24" s="4">
-        <v>2739.99</v>
+        <v>2728.96</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <v>2739.99</v>
+        <v>2728.96</v>
       </c>
       <c r="H24" s="4">
         <v>0.03</v>
       </c>
       <c r="I24" s="4">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J24" s="5">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -1350,22 +1354,22 @@
         <v>14</v>
       </c>
       <c r="E25" s="4">
-        <v>36685.96</v>
+        <v>34553.620000000003</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <v>36685.96</v>
+        <v>34553.620000000003</v>
       </c>
       <c r="H25" s="4">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="I25" s="4">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J25" s="5">
-        <v>173.87</v>
+        <v>171.06</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -1383,22 +1387,22 @@
         <v>15</v>
       </c>
       <c r="E26" s="4">
-        <v>40081.129999999997</v>
+        <v>39334.870000000003</v>
       </c>
       <c r="F26" s="4">
-        <v>6436.71</v>
+        <v>6324.43</v>
       </c>
       <c r="G26" s="4">
-        <v>33644.42</v>
+        <v>33010.44</v>
       </c>
       <c r="H26" s="4">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="I26" s="4">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="J26" s="5">
-        <v>63.12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -1515,22 +1519,22 @@
         <v>11</v>
       </c>
       <c r="E30" s="4">
-        <v>388262.98</v>
+        <v>383740.42</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="4">
-        <v>388262.98</v>
+        <v>383740.42</v>
       </c>
       <c r="H30" s="4">
-        <v>4.41</v>
+        <v>3.81</v>
       </c>
       <c r="I30" s="4">
-        <v>4298</v>
+        <v>4258</v>
       </c>
       <c r="J30" s="5">
-        <v>90.34</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -1548,22 +1552,22 @@
         <v>13</v>
       </c>
       <c r="E31" s="4">
-        <v>3368.15</v>
+        <v>3327.56</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
       <c r="G31" s="4">
-        <v>3368.15</v>
+        <v>3327.56</v>
       </c>
       <c r="H31" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I31" s="4">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="J31" s="5">
-        <v>7.78</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -1581,22 +1585,22 @@
         <v>14</v>
       </c>
       <c r="E32" s="4">
-        <v>33653.75</v>
+        <v>32196.400000000001</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
       <c r="G32" s="4">
-        <v>33653.75</v>
+        <v>32196.400000000001</v>
       </c>
       <c r="H32" s="4">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="I32" s="4">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J32" s="5">
-        <v>156.53</v>
+        <v>154.05000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -1614,22 +1618,22 @@
         <v>15</v>
       </c>
       <c r="E33" s="4">
-        <v>49785.5</v>
+        <v>49035.51</v>
       </c>
       <c r="F33" s="4">
-        <v>8065.4</v>
+        <v>8001.18</v>
       </c>
       <c r="G33" s="4">
-        <v>41720.1</v>
+        <v>41034.33</v>
       </c>
       <c r="H33" s="4">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="I33" s="4">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="J33" s="5">
-        <v>69.069999999999993</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -1689,7 +1693,7 @@
         <v>4133.7</v>
       </c>
       <c r="H35" s="4">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I35" s="4">
         <v>28</v>
@@ -1746,22 +1750,22 @@
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>407895.21</v>
+        <v>401473.08</v>
       </c>
       <c r="F37" s="4">
         <v>0</v>
       </c>
       <c r="G37" s="4">
-        <v>407895.21</v>
+        <v>401473.08</v>
       </c>
       <c r="H37" s="4">
-        <v>4.63</v>
+        <v>3.99</v>
       </c>
       <c r="I37" s="4">
-        <v>4167</v>
+        <v>4136</v>
       </c>
       <c r="J37" s="5">
-        <v>97.89</v>
+        <v>97.07</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -1779,22 +1783,22 @@
         <v>13</v>
       </c>
       <c r="E38" s="4">
-        <v>3031.72</v>
+        <v>3022.01</v>
       </c>
       <c r="F38" s="4">
         <v>0</v>
       </c>
       <c r="G38" s="4">
-        <v>3031.72</v>
+        <v>3022.01</v>
       </c>
       <c r="H38" s="4">
         <v>0.03</v>
       </c>
       <c r="I38" s="4">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J38" s="5">
-        <v>8.64</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -1812,22 +1816,22 @@
         <v>14</v>
       </c>
       <c r="E39" s="4">
-        <v>42844.14</v>
+        <v>42702.98</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
       </c>
       <c r="G39" s="4">
-        <v>42844.14</v>
+        <v>42702.98</v>
       </c>
       <c r="H39" s="4">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="I39" s="4">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J39" s="5">
-        <v>170.02</v>
+        <v>170.13</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -1845,22 +1849,22 @@
         <v>15</v>
       </c>
       <c r="E40" s="4">
-        <v>46625.49</v>
+        <v>45563.55</v>
       </c>
       <c r="F40" s="4">
-        <v>8499.8700000000008</v>
+        <v>8333.9699999999993</v>
       </c>
       <c r="G40" s="4">
-        <v>38125.620000000003</v>
+        <v>37229.58</v>
       </c>
       <c r="H40" s="4">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="I40" s="4">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="J40" s="5">
-        <v>62.2</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -1944,22 +1948,22 @@
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>410149.02</v>
+        <v>403738.46</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
       </c>
       <c r="G43" s="4">
-        <v>410149.02</v>
+        <v>403738.46</v>
       </c>
       <c r="H43" s="4">
-        <v>4.6500000000000004</v>
+        <v>4.01</v>
       </c>
       <c r="I43" s="4">
-        <v>4026</v>
+        <v>3992</v>
       </c>
       <c r="J43" s="5">
-        <v>101.88</v>
+        <v>101.14</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -1986,7 +1990,7 @@
         <v>3512.83</v>
       </c>
       <c r="H44" s="4">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I44" s="4">
         <v>431</v>
@@ -2010,22 +2014,22 @@
         <v>14</v>
       </c>
       <c r="E45" s="4">
-        <v>35113.019999999997</v>
+        <v>33512.199999999997</v>
       </c>
       <c r="F45" s="4">
         <v>0</v>
       </c>
       <c r="G45" s="4">
-        <v>35113.019999999997</v>
+        <v>33512.199999999997</v>
       </c>
       <c r="H45" s="4">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="I45" s="4">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J45" s="5">
-        <v>169.63</v>
+        <v>168.4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -2043,22 +2047,22 @@
         <v>15</v>
       </c>
       <c r="E46" s="4">
-        <v>43465.68</v>
+        <v>42987.87</v>
       </c>
       <c r="F46" s="4">
-        <v>6324.22</v>
+        <v>6323.35</v>
       </c>
       <c r="G46" s="4">
-        <v>37141.46</v>
+        <v>36664.519999999997</v>
       </c>
       <c r="H46" s="4">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="I46" s="4">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="J46" s="5">
-        <v>71.56</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -2208,22 +2212,22 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>884.65</v>
+        <v>373914.9</v>
       </c>
       <c r="F51" s="4">
         <v>0</v>
       </c>
       <c r="G51" s="4">
-        <v>884.65</v>
+        <v>373914.9</v>
       </c>
       <c r="H51" s="4">
-        <v>0.01</v>
+        <v>3.72</v>
       </c>
       <c r="I51" s="4">
-        <v>12</v>
+        <v>3733</v>
       </c>
       <c r="J51" s="5">
-        <v>73.72</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -2238,16 +2242,16 @@
         <v>29</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E52" s="4">
-        <v>20.18</v>
+        <v>307</v>
       </c>
       <c r="F52" s="4">
         <v>0</v>
       </c>
       <c r="G52" s="4">
-        <v>20.18</v>
+        <v>307</v>
       </c>
       <c r="H52" s="4">
         <v>0</v>
@@ -2256,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="5">
-        <v>20.18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -2271,223 +2275,223 @@
         <v>29</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E53" s="4">
-        <v>208.33</v>
+        <v>3723.57</v>
       </c>
       <c r="F53" s="4">
         <v>0</v>
       </c>
       <c r="G53" s="4">
-        <v>208.33</v>
+        <v>3723.57</v>
       </c>
       <c r="H53" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="4">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="J53" s="5">
-        <v>208.33</v>
+        <v>9.4499999999999993</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E54" s="4">
-        <v>674762.4</v>
+        <v>27765.99</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
       </c>
       <c r="G54" s="4">
-        <v>674762.4</v>
+        <v>27765.99</v>
       </c>
       <c r="H54" s="4">
-        <v>7.66</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I54" s="4">
-        <v>8236</v>
+        <v>202</v>
       </c>
       <c r="J54" s="5">
-        <v>81.93</v>
+        <v>137.46</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E55" s="4">
-        <v>3880.76</v>
+        <v>40163.910000000003</v>
       </c>
       <c r="F55" s="4">
-        <v>0</v>
+        <v>6712.95</v>
       </c>
       <c r="G55" s="4">
-        <v>3880.76</v>
+        <v>33450.959999999999</v>
       </c>
       <c r="H55" s="4">
-        <v>0.04</v>
+        <v>0.33</v>
       </c>
       <c r="I55" s="4">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="J55" s="5">
-        <v>7.79</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="str">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4">
+        <v>164.56</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4">
+        <v>164.56</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4">
         <v>1</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="4">
-        <v>38340.97</v>
-      </c>
-      <c r="F56" s="4">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4">
-        <v>38340.97</v>
-      </c>
-      <c r="H56" s="4">
-        <v>0.44</v>
-      </c>
-      <c r="I56" s="4">
-        <v>333</v>
-      </c>
       <c r="J56" s="5">
-        <v>115.14</v>
+        <v>164.56</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="str">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="4">
+        <v>61.03</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4">
+        <v>61.03</v>
+      </c>
+      <c r="H57" s="4">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4">
         <v>1</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" s="4">
-        <v>93070.24</v>
-      </c>
-      <c r="F57" s="4">
-        <v>22544.46</v>
-      </c>
-      <c r="G57" s="4">
-        <v>70525.78</v>
-      </c>
-      <c r="H57" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="I57" s="4">
-        <v>1461</v>
-      </c>
       <c r="J57" s="5">
-        <v>48.27</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E58" s="4">
-        <v>441.04</v>
+        <v>2534.7399999999998</v>
       </c>
       <c r="F58" s="4">
         <v>0</v>
       </c>
       <c r="G58" s="4">
-        <v>441.04</v>
+        <v>2534.7399999999998</v>
       </c>
       <c r="H58" s="4">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I58" s="4">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J58" s="5">
-        <v>441.04</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E59" s="4">
-        <v>3653.89</v>
+        <v>1314.38</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
       </c>
       <c r="G59" s="4">
-        <v>3653.89</v>
+        <v>1314.38</v>
       </c>
       <c r="H59" s="4">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I59" s="4">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J59" s="5">
-        <v>98.75</v>
+        <v>69.180000000000007</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -2502,228 +2506,228 @@
         <v>10</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E60" s="4">
-        <v>1644.48</v>
+        <v>671822.09</v>
       </c>
       <c r="F60" s="4">
         <v>0</v>
       </c>
       <c r="G60" s="4">
-        <v>1644.48</v>
+        <v>671822.09</v>
       </c>
       <c r="H60" s="4">
-        <v>0.02</v>
+        <v>6.68</v>
       </c>
       <c r="I60" s="4">
-        <v>25</v>
+        <v>8200</v>
       </c>
       <c r="J60" s="5">
-        <v>65.78</v>
+        <v>81.93</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E61" s="4">
-        <v>698521.38</v>
+        <v>3850.77</v>
       </c>
       <c r="F61" s="4">
         <v>0</v>
       </c>
       <c r="G61" s="4">
-        <v>698521.38</v>
+        <v>3850.77</v>
       </c>
       <c r="H61" s="4">
-        <v>7.93</v>
+        <v>0.04</v>
       </c>
       <c r="I61" s="4">
-        <v>8152</v>
+        <v>494</v>
       </c>
       <c r="J61" s="5">
-        <v>85.69</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E62" s="4">
-        <v>3713.66</v>
+        <v>37711.269999999997</v>
       </c>
       <c r="F62" s="4">
         <v>0</v>
       </c>
       <c r="G62" s="4">
-        <v>3713.66</v>
+        <v>37711.269999999997</v>
       </c>
       <c r="H62" s="4">
-        <v>0.04</v>
+        <v>0.37</v>
       </c>
       <c r="I62" s="4">
-        <v>517</v>
+        <v>329</v>
       </c>
       <c r="J62" s="5">
-        <v>7.18</v>
+        <v>114.62</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E63" s="4">
-        <v>41042.1</v>
+        <v>92819.14</v>
       </c>
       <c r="F63" s="4">
-        <v>0</v>
+        <v>22517.61</v>
       </c>
       <c r="G63" s="4">
-        <v>41042.1</v>
+        <v>70301.53</v>
       </c>
       <c r="H63" s="4">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="I63" s="4">
-        <v>305</v>
+        <v>1456</v>
       </c>
       <c r="J63" s="5">
-        <v>134.56</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E64" s="4">
-        <v>95064.21</v>
+        <v>441.04</v>
       </c>
       <c r="F64" s="4">
-        <v>22506.87</v>
+        <v>0</v>
       </c>
       <c r="G64" s="4">
-        <v>72557.34</v>
+        <v>441.04</v>
       </c>
       <c r="H64" s="4">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="I64" s="4">
-        <v>1402</v>
+        <v>1</v>
       </c>
       <c r="J64" s="5">
-        <v>51.75</v>
+        <v>441.04</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E65" s="4">
-        <v>55.96</v>
+        <v>3525.22</v>
       </c>
       <c r="F65" s="4">
         <v>0</v>
       </c>
       <c r="G65" s="4">
-        <v>55.96</v>
+        <v>3525.22</v>
       </c>
       <c r="H65" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I65" s="4">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J65" s="5">
-        <v>55.96</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E66" s="4">
-        <v>2943</v>
+        <v>1644.48</v>
       </c>
       <c r="F66" s="4">
         <v>0</v>
       </c>
       <c r="G66" s="4">
-        <v>2943</v>
+        <v>1644.48</v>
       </c>
       <c r="H66" s="4">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I66" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J66" s="5">
-        <v>105.11</v>
+        <v>65.78</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="str">
-        <f t="shared" ref="A67:A113" si="1">RIGHT(C67,1)</f>
+        <f t="shared" ref="A67:A124" si="1">RIGHT(C67,1)</f>
         <v>2</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -2733,223 +2737,223 @@
         <v>18</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>2455.25</v>
+        <v>696608.67</v>
       </c>
       <c r="F67" s="4">
         <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>2455.25</v>
+        <v>696608.67</v>
       </c>
       <c r="H67" s="4">
-        <v>0.03</v>
+        <v>6.92</v>
       </c>
       <c r="I67" s="4">
-        <v>39</v>
+        <v>8125</v>
       </c>
       <c r="J67" s="5">
-        <v>62.96</v>
+        <v>85.74</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E68" s="4">
-        <v>851510.25</v>
+        <v>3671.18</v>
       </c>
       <c r="F68" s="4">
         <v>0</v>
       </c>
       <c r="G68" s="4">
-        <v>851510.25</v>
+        <v>3671.18</v>
       </c>
       <c r="H68" s="4">
-        <v>9.66</v>
+        <v>0.04</v>
       </c>
       <c r="I68" s="4">
-        <v>9684</v>
+        <v>512</v>
       </c>
       <c r="J68" s="5">
-        <v>87.93</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E69" s="4">
-        <v>4674.12</v>
+        <v>40296.81</v>
       </c>
       <c r="F69" s="4">
         <v>0</v>
       </c>
       <c r="G69" s="4">
-        <v>4674.12</v>
+        <v>40296.81</v>
       </c>
       <c r="H69" s="4">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="I69" s="4">
-        <v>656</v>
+        <v>300</v>
       </c>
       <c r="J69" s="5">
-        <v>7.13</v>
+        <v>134.32</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E70" s="4">
-        <v>57214.36</v>
+        <v>94363.72</v>
       </c>
       <c r="F70" s="4">
-        <v>0</v>
+        <v>22470.02</v>
       </c>
       <c r="G70" s="4">
-        <v>57214.36</v>
+        <v>71893.7</v>
       </c>
       <c r="H70" s="4">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="I70" s="4">
-        <v>373</v>
+        <v>1396</v>
       </c>
       <c r="J70" s="5">
-        <v>153.38999999999999</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E71" s="4">
-        <v>112964.08</v>
+        <v>55.96</v>
       </c>
       <c r="F71" s="4">
-        <v>26690.03</v>
+        <v>0</v>
       </c>
       <c r="G71" s="4">
-        <v>86274.05</v>
+        <v>55.96</v>
       </c>
       <c r="H71" s="4">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I71" s="4">
-        <v>1602</v>
+        <v>1</v>
       </c>
       <c r="J71" s="5">
-        <v>53.85</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E72" s="4">
-        <v>103.76</v>
+        <v>2943</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
       </c>
       <c r="G72" s="4">
-        <v>103.76</v>
+        <v>2943</v>
       </c>
       <c r="H72" s="4">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I72" s="4">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J72" s="5">
-        <v>103.76</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E73" s="4">
-        <v>5938.26</v>
+        <v>2455.25</v>
       </c>
       <c r="F73" s="4">
         <v>0</v>
       </c>
       <c r="G73" s="4">
-        <v>5938.26</v>
+        <v>2455.25</v>
       </c>
       <c r="H73" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I73" s="4">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J73" s="5">
-        <v>123.71</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -2964,223 +2968,223 @@
         <v>19</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E74" s="4">
-        <v>2093.71</v>
+        <v>849305.14</v>
       </c>
       <c r="F74" s="4">
         <v>0</v>
       </c>
       <c r="G74" s="4">
-        <v>2093.71</v>
+        <v>849305.14</v>
       </c>
       <c r="H74" s="4">
-        <v>0.02</v>
+        <v>8.44</v>
       </c>
       <c r="I74" s="4">
-        <v>35</v>
+        <v>9662</v>
       </c>
       <c r="J74" s="5">
-        <v>59.82</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E75" s="4">
-        <v>725127.34</v>
+        <v>4621.12</v>
       </c>
       <c r="F75" s="4">
         <v>0</v>
       </c>
       <c r="G75" s="4">
-        <v>725127.34</v>
+        <v>4621.12</v>
       </c>
       <c r="H75" s="4">
-        <v>8.23</v>
+        <v>0.05</v>
       </c>
       <c r="I75" s="4">
-        <v>8281</v>
+        <v>650</v>
       </c>
       <c r="J75" s="5">
-        <v>87.57</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E76" s="4">
-        <v>4675.7</v>
+        <v>55641.3</v>
       </c>
       <c r="F76" s="4">
         <v>0</v>
       </c>
       <c r="G76" s="4">
-        <v>4675.7</v>
+        <v>55641.3</v>
       </c>
       <c r="H76" s="4">
-        <v>0.05</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I76" s="4">
-        <v>632</v>
+        <v>370</v>
       </c>
       <c r="J76" s="5">
-        <v>7.4</v>
+        <v>150.38</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E77" s="4">
-        <v>37628.54</v>
+        <v>111346.31</v>
       </c>
       <c r="F77" s="4">
-        <v>0</v>
+        <v>26690.03</v>
       </c>
       <c r="G77" s="4">
-        <v>37628.54</v>
+        <v>84656.28</v>
       </c>
       <c r="H77" s="4">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="I77" s="4">
-        <v>275</v>
+        <v>1587</v>
       </c>
       <c r="J77" s="5">
-        <v>136.83000000000001</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E78" s="4">
-        <v>99752.08</v>
+        <v>103.76</v>
       </c>
       <c r="F78" s="4">
-        <v>24044.36</v>
+        <v>0</v>
       </c>
       <c r="G78" s="4">
-        <v>75707.72</v>
+        <v>103.76</v>
       </c>
       <c r="H78" s="4">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I78" s="4">
-        <v>1459</v>
+        <v>1</v>
       </c>
       <c r="J78" s="5">
-        <v>51.89</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E79" s="4">
-        <v>291.57</v>
+        <v>5938.26</v>
       </c>
       <c r="F79" s="4">
         <v>0</v>
       </c>
       <c r="G79" s="4">
-        <v>291.57</v>
+        <v>5938.26</v>
       </c>
       <c r="H79" s="4">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I79" s="4">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J79" s="5">
-        <v>97.19</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E80" s="4">
-        <v>7.35</v>
+        <v>2093.71</v>
       </c>
       <c r="F80" s="4">
         <v>0</v>
       </c>
       <c r="G80" s="4">
-        <v>7.35</v>
+        <v>2093.71</v>
       </c>
       <c r="H80" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I80" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J80" s="5">
-        <v>7.35</v>
+        <v>59.82</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
@@ -3195,25 +3199,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>187.43</v>
+        <v>721565.24</v>
       </c>
       <c r="F81" s="4">
         <v>0</v>
       </c>
       <c r="G81" s="4">
-        <v>187.43</v>
+        <v>721565.24</v>
       </c>
       <c r="H81" s="4">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="I81" s="4">
-        <v>1</v>
+        <v>8268</v>
       </c>
       <c r="J81" s="5">
-        <v>187.43</v>
+        <v>87.27</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -3228,25 +3232,25 @@
         <v>20</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E82" s="4">
-        <v>3366.55</v>
+        <v>4653.5600000000004</v>
       </c>
       <c r="F82" s="4">
         <v>0</v>
       </c>
       <c r="G82" s="4">
-        <v>3366.55</v>
+        <v>4653.5600000000004</v>
       </c>
       <c r="H82" s="4">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I82" s="4">
-        <v>33</v>
+        <v>628</v>
       </c>
       <c r="J82" s="5">
-        <v>102.02</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -3261,223 +3265,223 @@
         <v>20</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E83" s="4">
-        <v>2148.54</v>
+        <v>37394.75</v>
       </c>
       <c r="F83" s="4">
         <v>0</v>
       </c>
       <c r="G83" s="4">
-        <v>2148.54</v>
+        <v>37394.75</v>
       </c>
       <c r="H83" s="4">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="I83" s="4">
-        <v>40</v>
+        <v>273</v>
       </c>
       <c r="J83" s="5">
-        <v>53.71</v>
+        <v>136.97999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E84" s="4">
-        <v>757197.58</v>
+        <v>99140.43</v>
       </c>
       <c r="F84" s="4">
-        <v>0</v>
+        <v>24006.61</v>
       </c>
       <c r="G84" s="4">
-        <v>757197.58</v>
+        <v>75133.820000000007</v>
       </c>
       <c r="H84" s="4">
-        <v>8.59</v>
+        <v>0.75</v>
       </c>
       <c r="I84" s="4">
-        <v>8700</v>
+        <v>1449</v>
       </c>
       <c r="J84" s="5">
-        <v>87.03</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E85" s="4">
-        <v>2750</v>
+        <v>291.57</v>
       </c>
       <c r="F85" s="4">
         <v>0</v>
       </c>
       <c r="G85" s="4">
-        <v>2750</v>
+        <v>291.57</v>
       </c>
       <c r="H85" s="4">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I85" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85" s="5">
-        <v>687.5</v>
+        <v>97.19</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E86" s="4">
-        <v>4433.8100000000004</v>
+        <v>7.35</v>
       </c>
       <c r="F86" s="4">
         <v>0</v>
       </c>
       <c r="G86" s="4">
-        <v>4433.8100000000004</v>
+        <v>7.35</v>
       </c>
       <c r="H86" s="4">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I86" s="4">
-        <v>601</v>
+        <v>1</v>
       </c>
       <c r="J86" s="5">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E87" s="4">
-        <v>42705.82</v>
+        <v>187.43</v>
       </c>
       <c r="F87" s="4">
         <v>0</v>
       </c>
       <c r="G87" s="4">
-        <v>42705.82</v>
+        <v>187.43</v>
       </c>
       <c r="H87" s="4">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="I87" s="4">
-        <v>292</v>
+        <v>1</v>
       </c>
       <c r="J87" s="5">
-        <v>146.25</v>
+        <v>187.43</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E88" s="4">
-        <v>109615.58</v>
+        <v>3366.55</v>
       </c>
       <c r="F88" s="4">
-        <v>26722.77</v>
+        <v>0</v>
       </c>
       <c r="G88" s="4">
-        <v>82892.81</v>
+        <v>3366.55</v>
       </c>
       <c r="H88" s="4">
-        <v>0.94</v>
+        <v>0.03</v>
       </c>
       <c r="I88" s="4">
-        <v>1569</v>
+        <v>33</v>
       </c>
       <c r="J88" s="5">
-        <v>52.83</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E89" s="4">
-        <v>191.98</v>
+        <v>2148.54</v>
       </c>
       <c r="F89" s="4">
         <v>0</v>
       </c>
       <c r="G89" s="4">
-        <v>191.98</v>
+        <v>2148.54</v>
       </c>
       <c r="H89" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I89" s="4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J89" s="5">
-        <v>32</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -3492,25 +3496,25 @@
         <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E90" s="4">
-        <v>216.57</v>
+        <v>756137.28</v>
       </c>
       <c r="F90" s="4">
         <v>0</v>
       </c>
       <c r="G90" s="4">
-        <v>216.57</v>
+        <v>756137.28</v>
       </c>
       <c r="H90" s="4">
-        <v>0</v>
+        <v>7.52</v>
       </c>
       <c r="I90" s="4">
-        <v>4</v>
+        <v>8685</v>
       </c>
       <c r="J90" s="5">
-        <v>54.14</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -3525,25 +3529,25 @@
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E91" s="4">
-        <v>4202.47</v>
+        <v>2750</v>
       </c>
       <c r="F91" s="4">
         <v>0</v>
       </c>
       <c r="G91" s="4">
-        <v>4202.47</v>
+        <v>2750</v>
       </c>
       <c r="H91" s="4">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I91" s="4">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J91" s="5">
-        <v>110.59</v>
+        <v>687.5</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
@@ -3558,154 +3562,154 @@
         <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E92" s="4">
-        <v>2016.64</v>
+        <v>4428.8100000000004</v>
       </c>
       <c r="F92" s="4">
         <v>0</v>
       </c>
       <c r="G92" s="4">
-        <v>2016.64</v>
+        <v>4428.8100000000004</v>
       </c>
       <c r="H92" s="4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I92" s="4">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="J92" s="5">
-        <v>63.02</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E93" s="4">
-        <v>747057.91</v>
+        <v>42258.52</v>
       </c>
       <c r="F93" s="4">
         <v>0</v>
       </c>
       <c r="G93" s="4">
-        <v>747057.91</v>
+        <v>42258.52</v>
       </c>
       <c r="H93" s="4">
-        <v>8.48</v>
+        <v>0.42</v>
       </c>
       <c r="I93" s="4">
-        <v>8425</v>
+        <v>289</v>
       </c>
       <c r="J93" s="5">
-        <v>88.67</v>
+        <v>146.22</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E94" s="4">
-        <v>4308.8999999999996</v>
+        <v>109524.57</v>
       </c>
       <c r="F94" s="4">
-        <v>0</v>
+        <v>26703.17</v>
       </c>
       <c r="G94" s="4">
-        <v>4308.8999999999996</v>
+        <v>82821.399999999994</v>
       </c>
       <c r="H94" s="4">
-        <v>0.05</v>
+        <v>0.82</v>
       </c>
       <c r="I94" s="4">
-        <v>572</v>
+        <v>1566</v>
       </c>
       <c r="J94" s="5">
-        <v>7.53</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="str">
         <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="4">
+        <v>191.98</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="4">
+        <v>191.98</v>
+      </c>
+      <c r="H95" s="4">
+        <v>0</v>
+      </c>
+      <c r="I95" s="4">
         <v>6</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" s="4">
-        <v>38668.19</v>
-      </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-      <c r="G95" s="4">
-        <v>38668.19</v>
-      </c>
-      <c r="H95" s="4">
-        <v>0.44</v>
-      </c>
-      <c r="I95" s="4">
-        <v>272</v>
-      </c>
       <c r="J95" s="5">
-        <v>142.16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E96" s="4">
-        <v>104131.34</v>
+        <v>216.57</v>
       </c>
       <c r="F96" s="4">
-        <v>23789.14</v>
+        <v>0</v>
       </c>
       <c r="G96" s="4">
-        <v>80342.2</v>
+        <v>216.57</v>
       </c>
       <c r="H96" s="4">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="I96" s="4">
-        <v>1484</v>
+        <v>4</v>
       </c>
       <c r="J96" s="5">
         <v>54.14</v>
@@ -3714,67 +3718,67 @@
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E97" s="4">
-        <v>1506.56</v>
+        <v>4202.47</v>
       </c>
       <c r="F97" s="4">
         <v>0</v>
       </c>
       <c r="G97" s="4">
-        <v>1506.56</v>
+        <v>4202.47</v>
       </c>
       <c r="H97" s="4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I97" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="J97" s="5">
-        <v>71.739999999999995</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E98" s="4">
-        <v>439.16</v>
+        <v>2016.64</v>
       </c>
       <c r="F98" s="4">
         <v>0</v>
       </c>
       <c r="G98" s="4">
-        <v>439.16</v>
+        <v>2016.64</v>
       </c>
       <c r="H98" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I98" s="4">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J98" s="5">
-        <v>219.58</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
@@ -3789,25 +3793,25 @@
         <v>23</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>3950.13</v>
+        <v>745920.06</v>
       </c>
       <c r="F99" s="4">
         <v>0</v>
       </c>
       <c r="G99" s="4">
-        <v>3950.13</v>
+        <v>745920.06</v>
       </c>
       <c r="H99" s="4">
-        <v>0.04</v>
+        <v>7.41</v>
       </c>
       <c r="I99" s="4">
-        <v>35</v>
+        <v>8419</v>
       </c>
       <c r="J99" s="5">
-        <v>112.86</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
@@ -3822,223 +3826,223 @@
         <v>23</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E100" s="4">
-        <v>8981.17</v>
+        <v>4268.91</v>
       </c>
       <c r="F100" s="4">
         <v>0</v>
       </c>
       <c r="G100" s="4">
-        <v>8981.17</v>
+        <v>4268.91</v>
       </c>
       <c r="H100" s="4">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I100" s="4">
-        <v>47</v>
+        <v>567</v>
       </c>
       <c r="J100" s="5">
-        <v>191.09</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E101" s="4">
-        <v>744338.73</v>
+        <v>38280.120000000003</v>
       </c>
       <c r="F101" s="4">
         <v>0</v>
       </c>
       <c r="G101" s="4">
-        <v>744338.73</v>
+        <v>38280.120000000003</v>
       </c>
       <c r="H101" s="4">
-        <v>8.4499999999999993</v>
+        <v>0.38</v>
       </c>
       <c r="I101" s="4">
-        <v>8321</v>
+        <v>270</v>
       </c>
       <c r="J101" s="5">
-        <v>89.45</v>
+        <v>141.78</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E102" s="4">
-        <v>3959.54</v>
+        <v>102767.41</v>
       </c>
       <c r="F102" s="4">
-        <v>0</v>
+        <v>23788.99</v>
       </c>
       <c r="G102" s="4">
-        <v>3959.54</v>
+        <v>78978.42</v>
       </c>
       <c r="H102" s="4">
-        <v>0.04</v>
+        <v>0.79</v>
       </c>
       <c r="I102" s="4">
-        <v>536</v>
+        <v>1477</v>
       </c>
       <c r="J102" s="5">
-        <v>7.39</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E103" s="4">
-        <v>43058.99</v>
+        <v>1492.15</v>
       </c>
       <c r="F103" s="4">
         <v>0</v>
       </c>
       <c r="G103" s="4">
-        <v>43058.99</v>
+        <v>1492.15</v>
       </c>
       <c r="H103" s="4">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="I103" s="4">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="J103" s="5">
-        <v>173.62</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E104" s="4">
-        <v>92036.49</v>
+        <v>439.16</v>
       </c>
       <c r="F104" s="4">
-        <v>23074.9</v>
+        <v>0</v>
       </c>
       <c r="G104" s="4">
-        <v>68961.59</v>
+        <v>439.16</v>
       </c>
       <c r="H104" s="4">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="I104" s="4">
-        <v>1296</v>
+        <v>2</v>
       </c>
       <c r="J104" s="5">
-        <v>53.21</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E105" s="4">
-        <v>273.26</v>
+        <v>3950.13</v>
       </c>
       <c r="F105" s="4">
         <v>0</v>
       </c>
       <c r="G105" s="4">
-        <v>273.26</v>
+        <v>3950.13</v>
       </c>
       <c r="H105" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I105" s="4">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="J105" s="5">
-        <v>39.04</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E106" s="4">
-        <v>20.52</v>
+        <v>5480.02</v>
       </c>
       <c r="F106" s="4">
         <v>0</v>
       </c>
       <c r="G106" s="4">
-        <v>20.52</v>
+        <v>5480.02</v>
       </c>
       <c r="H106" s="4">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I106" s="4">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J106" s="5">
-        <v>20.52</v>
+        <v>119.13</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
@@ -4053,25 +4057,25 @@
         <v>27</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>4376.3599999999997</v>
+        <v>743586.03</v>
       </c>
       <c r="F107" s="4">
         <v>0</v>
       </c>
       <c r="G107" s="4">
-        <v>4376.3599999999997</v>
+        <v>743586.03</v>
       </c>
       <c r="H107" s="4">
-        <v>0.05</v>
+        <v>7.39</v>
       </c>
       <c r="I107" s="4">
-        <v>38</v>
+        <v>8311</v>
       </c>
       <c r="J107" s="5">
-        <v>115.17</v>
+        <v>89.47</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -4086,190 +4090,553 @@
         <v>27</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E108" s="4">
-        <v>2172.27</v>
+        <v>3937.16</v>
       </c>
       <c r="F108" s="4">
         <v>0</v>
       </c>
       <c r="G108" s="4">
-        <v>2172.27</v>
+        <v>3937.16</v>
       </c>
       <c r="H108" s="4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I108" s="4">
-        <v>38</v>
+        <v>530</v>
       </c>
       <c r="J108" s="5">
-        <v>57.17</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E109" s="4">
-        <v>2101.6999999999998</v>
+        <v>42910.83</v>
       </c>
       <c r="F109" s="4">
         <v>0</v>
       </c>
       <c r="G109" s="4">
-        <v>2101.6999999999998</v>
+        <v>42910.83</v>
       </c>
       <c r="H109" s="4">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
       <c r="I109" s="4">
-        <v>28</v>
+        <v>246</v>
       </c>
       <c r="J109" s="5">
-        <v>75.06</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E110" s="4">
-        <v>34.86</v>
+        <v>90953.279999999999</v>
       </c>
       <c r="F110" s="4">
-        <v>0</v>
+        <v>23074.9</v>
       </c>
       <c r="G110" s="4">
-        <v>34.86</v>
+        <v>67878.38</v>
       </c>
       <c r="H110" s="4">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I110" s="4">
-        <v>6</v>
+        <v>1288</v>
       </c>
       <c r="J110" s="5">
-        <v>5.81</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E111" s="4">
-        <v>44.9</v>
+        <v>273.26</v>
       </c>
       <c r="F111" s="4">
         <v>0</v>
       </c>
       <c r="G111" s="4">
-        <v>44.9</v>
+        <v>273.26</v>
       </c>
       <c r="H111" s="4">
         <v>0</v>
       </c>
       <c r="I111" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J111" s="5">
-        <v>44.9</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E112" s="4">
-        <v>211.5</v>
+        <v>20.52</v>
       </c>
       <c r="F112" s="4">
-        <v>111.82</v>
+        <v>0</v>
       </c>
       <c r="G112" s="4">
-        <v>99.68</v>
+        <v>20.52</v>
       </c>
       <c r="H112" s="4">
         <v>0</v>
       </c>
       <c r="I112" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J112" s="5">
-        <v>19.940000000000001</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E113" s="4">
-        <v>109.96</v>
+        <v>4376.3599999999997</v>
       </c>
       <c r="F113" s="4">
         <v>0</v>
       </c>
       <c r="G113" s="4">
-        <v>109.96</v>
+        <v>4376.3599999999997</v>
       </c>
       <c r="H113" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I113" s="4">
+        <v>38</v>
+      </c>
+      <c r="J113" s="5">
+        <v>115.17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="4">
+        <v>2172.27</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4">
+        <v>2172.27</v>
+      </c>
+      <c r="H114" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I114" s="4">
+        <v>38</v>
+      </c>
+      <c r="J114" s="5">
+        <v>57.17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="4">
+        <v>733515.66</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4">
+        <v>733515.66</v>
+      </c>
+      <c r="H115" s="4">
+        <v>7.29</v>
+      </c>
+      <c r="I115" s="4">
+        <v>8470</v>
+      </c>
+      <c r="J115" s="5">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="4">
+        <v>420</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="4">
+        <v>420</v>
+      </c>
+      <c r="H116" s="4">
+        <v>0</v>
+      </c>
+      <c r="I116" s="4">
         <v>1</v>
       </c>
-      <c r="J113" s="5">
-        <v>109.96</v>
+      <c r="J116" s="5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="4">
+        <v>4708.91</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>4708.91</v>
+      </c>
+      <c r="H117" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I117" s="4">
+        <v>544</v>
+      </c>
+      <c r="J117" s="5">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="4">
+        <v>47389.75</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4">
+        <v>47389.75</v>
+      </c>
+      <c r="H118" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="I118" s="4">
+        <v>255</v>
+      </c>
+      <c r="J118" s="5">
+        <v>185.84</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" s="4">
+        <v>95061.47</v>
+      </c>
+      <c r="F119" s="4">
+        <v>21456.37</v>
+      </c>
+      <c r="G119" s="4">
+        <v>73605.100000000006</v>
+      </c>
+      <c r="H119" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="I119" s="4">
+        <v>1368</v>
+      </c>
+      <c r="J119" s="5">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="4">
+        <v>566.35</v>
+      </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="4">
+        <v>566.35</v>
+      </c>
+      <c r="H120" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I120" s="4">
+        <v>5</v>
+      </c>
+      <c r="J120" s="5">
+        <v>113.27</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121" s="4">
+        <v>498.21</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4">
+        <v>498.21</v>
+      </c>
+      <c r="H121" s="4">
+        <v>0</v>
+      </c>
+      <c r="I121" s="4">
+        <v>14</v>
+      </c>
+      <c r="J121" s="5">
+        <v>35.590000000000003</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122" s="4">
+        <v>97.37</v>
+      </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4">
+        <v>97.37</v>
+      </c>
+      <c r="H122" s="4">
+        <v>0</v>
+      </c>
+      <c r="I122" s="4">
+        <v>1</v>
+      </c>
+      <c r="J122" s="5">
+        <v>97.37</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" s="4">
+        <v>5155.37</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>5155.37</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I123" s="4">
+        <v>48</v>
+      </c>
+      <c r="J123" s="5">
+        <v>107.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="4">
+        <v>3329.05</v>
+      </c>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4">
+        <v>3329.05</v>
+      </c>
+      <c r="H124" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I124" s="4">
+        <v>45</v>
+      </c>
+      <c r="J124" s="5">
+        <v>73.98</v>
       </c>
     </row>
   </sheetData>
